--- a/Test Results/Excel/Automation_Test_Report.xlsx
+++ b/Test Results/Excel/Automation_Test_Report.xlsx
@@ -1,15 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_AC139CF75D6C2DD52BC655DC3B2EB88BB27680A9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D897179-F72A-4A07-95E0-ACE92B1A0F4B}"/>
+  <bookViews>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Executed Test Cases" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Passed Tests" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Failed Tests" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Skipped Tests" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Execution Metrics" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Defect Summary" state="visible" r:id="rId9"/>
+    <sheet name="Executed Test Cases" sheetId="1" r:id="rId1"/>
+    <sheet name="Passed Tests" sheetId="2" r:id="rId2"/>
+    <sheet name="Failed Tests" sheetId="3" r:id="rId3"/>
+    <sheet name="Skipped Tests" sheetId="4" r:id="rId4"/>
+    <sheet name="Execution Metrics" sheetId="5" r:id="rId5"/>
+    <sheet name="Defect Summary" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -3009,30 +3013,38 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFF"/>
+      <sz val="11"/>
+      <color rgb="FF2E7D32"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="2E7D32"/>
+      <sz val="11"/>
+      <color rgb="FFC62828"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="C62828"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="F57F17"/>
+      <sz val="11"/>
+      <color rgb="FFF57F17"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="9">
@@ -3044,37 +3056,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="1565D8"/>
+        <fgColor rgb="FF1565D8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="E8F5E9"/>
+        <fgColor rgb="FFE8F5E9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEBEE"/>
+        <fgColor rgb="FFFFEBEE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8E1"/>
+        <fgColor rgb="FFFFF8E1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="2E7D32"/>
+        <fgColor rgb="FF2E7D32"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="C62828"/>
+        <fgColor rgb="FFC62828"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="F57F17"/>
+        <fgColor rgb="FFF57F17"/>
       </patternFill>
     </fill>
   </fills>
@@ -3437,9 +3449,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F471"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -3449,7 +3461,7 @@
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3469,7 +3481,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -3489,7 +3501,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -3509,7 +3521,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -3529,7 +3541,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -3549,7 +3561,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -3569,7 +3581,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -3589,7 +3601,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -3609,7 +3621,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -3629,7 +3641,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -3649,7 +3661,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -3669,7 +3681,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -3689,7 +3701,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -3709,7 +3721,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -3729,7 +3741,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -3749,7 +3761,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -3769,7 +3781,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -3789,7 +3801,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -3809,7 +3821,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -3829,7 +3841,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -3849,7 +3861,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -3869,7 +3881,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -3889,7 +3901,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>52</v>
       </c>
@@ -3909,7 +3921,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -3929,7 +3941,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -3949,7 +3961,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -3969,7 +3981,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -3989,7 +4001,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>62</v>
       </c>
@@ -4009,7 +4021,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>64</v>
       </c>
@@ -4029,7 +4041,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -4049,7 +4061,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>68</v>
       </c>
@@ -4069,7 +4081,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>70</v>
       </c>
@@ -4089,7 +4101,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>72</v>
       </c>
@@ -4109,7 +4121,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>74</v>
       </c>
@@ -4129,7 +4141,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>76</v>
       </c>
@@ -4149,7 +4161,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>78</v>
       </c>
@@ -4169,7 +4181,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>80</v>
       </c>
@@ -4189,7 +4201,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>82</v>
       </c>
@@ -4209,7 +4221,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>84</v>
       </c>
@@ -4229,7 +4241,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>86</v>
       </c>
@@ -4249,7 +4261,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>88</v>
       </c>
@@ -4269,7 +4281,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>90</v>
       </c>
@@ -4289,7 +4301,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>94</v>
       </c>
@@ -4309,7 +4321,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>96</v>
       </c>
@@ -4329,7 +4341,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>98</v>
       </c>
@@ -4349,7 +4361,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>100</v>
       </c>
@@ -4369,7 +4381,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>102</v>
       </c>
@@ -4389,7 +4401,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>104</v>
       </c>
@@ -4409,7 +4421,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>106</v>
       </c>
@@ -4429,7 +4441,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>108</v>
       </c>
@@ -4449,7 +4461,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>110</v>
       </c>
@@ -4469,7 +4481,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>112</v>
       </c>
@@ -4489,7 +4501,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>114</v>
       </c>
@@ -4509,7 +4521,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>116</v>
       </c>
@@ -4529,7 +4541,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>118</v>
       </c>
@@ -4549,7 +4561,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>120</v>
       </c>
@@ -4569,7 +4581,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>122</v>
       </c>
@@ -4589,7 +4601,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>124</v>
       </c>
@@ -4609,7 +4621,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>126</v>
       </c>
@@ -4629,7 +4641,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>128</v>
       </c>
@@ -4649,7 +4661,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>130</v>
       </c>
@@ -4669,7 +4681,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>132</v>
       </c>
@@ -4689,7 +4701,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>134</v>
       </c>
@@ -4709,7 +4721,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>136</v>
       </c>
@@ -4729,7 +4741,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>138</v>
       </c>
@@ -4749,7 +4761,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>140</v>
       </c>
@@ -4769,7 +4781,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>142</v>
       </c>
@@ -4789,7 +4801,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>144</v>
       </c>
@@ -4809,7 +4821,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>146</v>
       </c>
@@ -4829,7 +4841,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>148</v>
       </c>
@@ -4849,7 +4861,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>150</v>
       </c>
@@ -4869,7 +4881,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>152</v>
       </c>
@@ -4889,7 +4901,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>154</v>
       </c>
@@ -4909,7 +4921,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>156</v>
       </c>
@@ -4929,7 +4941,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>158</v>
       </c>
@@ -4949,7 +4961,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>160</v>
       </c>
@@ -4969,7 +4981,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>162</v>
       </c>
@@ -4989,7 +5001,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>164</v>
       </c>
@@ -5009,7 +5021,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>166</v>
       </c>
@@ -5029,7 +5041,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>168</v>
       </c>
@@ -5049,7 +5061,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>170</v>
       </c>
@@ -5069,7 +5081,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>172</v>
       </c>
@@ -5089,7 +5101,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>176</v>
       </c>
@@ -5109,7 +5121,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>178</v>
       </c>
@@ -5129,7 +5141,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>180</v>
       </c>
@@ -5149,7 +5161,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>182</v>
       </c>
@@ -5169,7 +5181,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>184</v>
       </c>
@@ -5189,7 +5201,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>186</v>
       </c>
@@ -5209,7 +5221,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>188</v>
       </c>
@@ -5229,7 +5241,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>190</v>
       </c>
@@ -5249,7 +5261,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>192</v>
       </c>
@@ -5269,7 +5281,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>194</v>
       </c>
@@ -5289,7 +5301,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>196</v>
       </c>
@@ -5309,7 +5321,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>198</v>
       </c>
@@ -5329,7 +5341,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>200</v>
       </c>
@@ -5349,7 +5361,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>202</v>
       </c>
@@ -5369,7 +5381,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>204</v>
       </c>
@@ -5389,7 +5401,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>206</v>
       </c>
@@ -5409,7 +5421,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>208</v>
       </c>
@@ -5429,7 +5441,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>210</v>
       </c>
@@ -5449,7 +5461,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>212</v>
       </c>
@@ -5469,7 +5481,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>214</v>
       </c>
@@ -5489,7 +5501,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>216</v>
       </c>
@@ -5509,7 +5521,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>218</v>
       </c>
@@ -5529,7 +5541,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>220</v>
       </c>
@@ -5549,7 +5561,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>222</v>
       </c>
@@ -5569,7 +5581,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>224</v>
       </c>
@@ -5589,7 +5601,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>226</v>
       </c>
@@ -5609,7 +5621,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>228</v>
       </c>
@@ -5629,7 +5641,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>230</v>
       </c>
@@ -5649,7 +5661,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>232</v>
       </c>
@@ -5669,7 +5681,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>234</v>
       </c>
@@ -5689,7 +5701,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>237</v>
       </c>
@@ -5709,7 +5721,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>239</v>
       </c>
@@ -5729,7 +5741,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>241</v>
       </c>
@@ -5749,7 +5761,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>243</v>
       </c>
@@ -5769,7 +5781,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>245</v>
       </c>
@@ -5789,7 +5801,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>247</v>
       </c>
@@ -5809,7 +5821,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>249</v>
       </c>
@@ -5829,7 +5841,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>251</v>
       </c>
@@ -5849,7 +5861,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>253</v>
       </c>
@@ -5869,7 +5881,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>255</v>
       </c>
@@ -5889,7 +5901,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>257</v>
       </c>
@@ -5909,7 +5921,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>259</v>
       </c>
@@ -5929,7 +5941,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>261</v>
       </c>
@@ -5949,7 +5961,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>263</v>
       </c>
@@ -5969,7 +5981,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>265</v>
       </c>
@@ -5989,7 +6001,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>267</v>
       </c>
@@ -6009,7 +6021,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>269</v>
       </c>
@@ -6029,7 +6041,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>271</v>
       </c>
@@ -6049,7 +6061,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>273</v>
       </c>
@@ -6069,7 +6081,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>275</v>
       </c>
@@ -6089,7 +6101,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>277</v>
       </c>
@@ -6109,7 +6121,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>279</v>
       </c>
@@ -6129,7 +6141,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>281</v>
       </c>
@@ -6149,7 +6161,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>283</v>
       </c>
@@ -6169,7 +6181,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>285</v>
       </c>
@@ -6189,7 +6201,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>287</v>
       </c>
@@ -6209,7 +6221,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>289</v>
       </c>
@@ -6229,7 +6241,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>291</v>
       </c>
@@ -6249,7 +6261,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>293</v>
       </c>
@@ -6269,7 +6281,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>295</v>
       </c>
@@ -6289,7 +6301,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>297</v>
       </c>
@@ -6309,7 +6321,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>299</v>
       </c>
@@ -6329,7 +6341,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>301</v>
       </c>
@@ -6349,7 +6361,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>303</v>
       </c>
@@ -6369,7 +6381,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>305</v>
       </c>
@@ -6389,7 +6401,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>307</v>
       </c>
@@ -6409,7 +6421,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>309</v>
       </c>
@@ -6429,7 +6441,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>311</v>
       </c>
@@ -6449,7 +6461,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>313</v>
       </c>
@@ -6469,7 +6481,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>315</v>
       </c>
@@ -6489,7 +6501,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>317</v>
       </c>
@@ -6509,7 +6521,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>319</v>
       </c>
@@ -6529,7 +6541,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>321</v>
       </c>
@@ -6549,7 +6561,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>323</v>
       </c>
@@ -6569,7 +6581,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>325</v>
       </c>
@@ -6589,7 +6601,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>327</v>
       </c>
@@ -6609,7 +6621,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>329</v>
       </c>
@@ -6629,7 +6641,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>331</v>
       </c>
@@ -6649,7 +6661,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>333</v>
       </c>
@@ -6669,7 +6681,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>335</v>
       </c>
@@ -6689,7 +6701,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>339</v>
       </c>
@@ -6709,7 +6721,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>341</v>
       </c>
@@ -6729,7 +6741,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>343</v>
       </c>
@@ -6749,7 +6761,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>345</v>
       </c>
@@ -6769,7 +6781,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>347</v>
       </c>
@@ -6789,7 +6801,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>349</v>
       </c>
@@ -6809,7 +6821,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>351</v>
       </c>
@@ -6829,7 +6841,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>353</v>
       </c>
@@ -6849,7 +6861,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>355</v>
       </c>
@@ -6869,7 +6881,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>357</v>
       </c>
@@ -6889,7 +6901,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>359</v>
       </c>
@@ -6909,7 +6921,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>361</v>
       </c>
@@ -6929,7 +6941,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>363</v>
       </c>
@@ -6949,7 +6961,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>365</v>
       </c>
@@ -6969,7 +6981,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>367</v>
       </c>
@@ -6989,7 +7001,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>369</v>
       </c>
@@ -7009,7 +7021,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>371</v>
       </c>
@@ -7029,7 +7041,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>373</v>
       </c>
@@ -7049,7 +7061,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>375</v>
       </c>
@@ -7069,7 +7081,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>377</v>
       </c>
@@ -7089,7 +7101,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>379</v>
       </c>
@@ -7109,7 +7121,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>381</v>
       </c>
@@ -7129,7 +7141,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>383</v>
       </c>
@@ -7149,7 +7161,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>385</v>
       </c>
@@ -7169,7 +7181,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>387</v>
       </c>
@@ -7189,7 +7201,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>389</v>
       </c>
@@ -7209,7 +7221,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>391</v>
       </c>
@@ -7229,7 +7241,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>393</v>
       </c>
@@ -7249,7 +7261,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>395</v>
       </c>
@@ -7269,7 +7281,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>397</v>
       </c>
@@ -7289,7 +7301,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>399</v>
       </c>
@@ -7309,7 +7321,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>401</v>
       </c>
@@ -7329,7 +7341,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>403</v>
       </c>
@@ -7349,7 +7361,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>405</v>
       </c>
@@ -7369,7 +7381,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>407</v>
       </c>
@@ -7389,7 +7401,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
         <v>409</v>
       </c>
@@ -7409,7 +7421,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
         <v>411</v>
       </c>
@@ -7429,7 +7441,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>413</v>
       </c>
@@ -7449,7 +7461,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>415</v>
       </c>
@@ -7469,7 +7481,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
         <v>417</v>
       </c>
@@ -7489,7 +7501,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
         <v>419</v>
       </c>
@@ -7509,7 +7521,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
         <v>421</v>
       </c>
@@ -7529,7 +7541,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
         <v>423</v>
       </c>
@@ -7549,7 +7561,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
         <v>425</v>
       </c>
@@ -7569,7 +7581,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
         <v>427</v>
       </c>
@@ -7589,7 +7601,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
         <v>429</v>
       </c>
@@ -7609,7 +7621,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
         <v>431</v>
       </c>
@@ -7629,7 +7641,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
         <v>433</v>
       </c>
@@ -7649,7 +7661,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
         <v>435</v>
       </c>
@@ -7669,7 +7681,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
         <v>437</v>
       </c>
@@ -7689,7 +7701,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
         <v>440</v>
       </c>
@@ -7709,7 +7721,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
         <v>442</v>
       </c>
@@ -7729,7 +7741,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
         <v>444</v>
       </c>
@@ -7749,7 +7761,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
         <v>446</v>
       </c>
@@ -7769,7 +7781,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
         <v>448</v>
       </c>
@@ -7789,7 +7801,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
         <v>450</v>
       </c>
@@ -7809,7 +7821,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
         <v>452</v>
       </c>
@@ -7829,7 +7841,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
         <v>454</v>
       </c>
@@ -7849,7 +7861,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
         <v>456</v>
       </c>
@@ -7869,7 +7881,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
         <v>458</v>
       </c>
@@ -7889,7 +7901,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
         <v>460</v>
       </c>
@@ -7909,7 +7921,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
         <v>462</v>
       </c>
@@ -7929,7 +7941,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
         <v>464</v>
       </c>
@@ -7949,7 +7961,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
         <v>466</v>
       </c>
@@ -7969,7 +7981,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
         <v>468</v>
       </c>
@@ -7989,7 +8001,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
         <v>470</v>
       </c>
@@ -8009,7 +8021,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
         <v>472</v>
       </c>
@@ -8029,7 +8041,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
         <v>474</v>
       </c>
@@ -8049,7 +8061,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
         <v>476</v>
       </c>
@@ -8069,7 +8081,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
         <v>478</v>
       </c>
@@ -8089,7 +8101,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
         <v>480</v>
       </c>
@@ -8109,7 +8121,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A234" t="s">
         <v>482</v>
       </c>
@@ -8129,7 +8141,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
         <v>484</v>
       </c>
@@ -8149,7 +8161,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A236" t="s">
         <v>486</v>
       </c>
@@ -8169,7 +8181,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
         <v>488</v>
       </c>
@@ -8189,7 +8201,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A238" t="s">
         <v>490</v>
       </c>
@@ -8209,7 +8221,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A239" t="s">
         <v>492</v>
       </c>
@@ -8229,7 +8241,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A240" t="s">
         <v>494</v>
       </c>
@@ -8249,7 +8261,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
         <v>496</v>
       </c>
@@ -8269,7 +8281,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
         <v>498</v>
       </c>
@@ -8289,7 +8301,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
         <v>500</v>
       </c>
@@ -8309,7 +8321,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
         <v>502</v>
       </c>
@@ -8329,7 +8341,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
         <v>504</v>
       </c>
@@ -8349,7 +8361,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A246" t="s">
         <v>506</v>
       </c>
@@ -8369,7 +8381,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
         <v>508</v>
       </c>
@@ -8389,7 +8401,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
         <v>510</v>
       </c>
@@ -8409,7 +8421,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
         <v>512</v>
       </c>
@@ -8429,7 +8441,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
         <v>514</v>
       </c>
@@ -8449,7 +8461,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
         <v>516</v>
       </c>
@@ -8469,7 +8481,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
         <v>518</v>
       </c>
@@ -8489,7 +8501,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
         <v>520</v>
       </c>
@@ -8509,7 +8521,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A254" t="s">
         <v>522</v>
       </c>
@@ -8529,7 +8541,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
         <v>524</v>
       </c>
@@ -8549,7 +8561,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A256" t="s">
         <v>526</v>
       </c>
@@ -8569,7 +8581,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
         <v>528</v>
       </c>
@@ -8589,7 +8601,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A258" t="s">
         <v>530</v>
       </c>
@@ -8609,7 +8621,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
         <v>532</v>
       </c>
@@ -8629,7 +8641,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
         <v>534</v>
       </c>
@@ -8649,7 +8661,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
         <v>536</v>
       </c>
@@ -8669,7 +8681,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
         <v>538</v>
       </c>
@@ -8689,7 +8701,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A263" t="s">
         <v>541</v>
       </c>
@@ -8709,7 +8721,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A264" t="s">
         <v>543</v>
       </c>
@@ -8729,7 +8741,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
         <v>545</v>
       </c>
@@ -8749,7 +8761,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
         <v>547</v>
       </c>
@@ -8769,7 +8781,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A267" t="s">
         <v>549</v>
       </c>
@@ -8789,7 +8801,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
         <v>551</v>
       </c>
@@ -8809,7 +8821,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A269" t="s">
         <v>553</v>
       </c>
@@ -8829,7 +8841,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A270" t="s">
         <v>555</v>
       </c>
@@ -8849,7 +8861,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
         <v>557</v>
       </c>
@@ -8869,7 +8881,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A272" t="s">
         <v>559</v>
       </c>
@@ -8889,7 +8901,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
         <v>561</v>
       </c>
@@ -8909,7 +8921,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A274" t="s">
         <v>563</v>
       </c>
@@ -8929,7 +8941,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A275" t="s">
         <v>565</v>
       </c>
@@ -8949,7 +8961,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A276" t="s">
         <v>567</v>
       </c>
@@ -8969,7 +8981,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
         <v>569</v>
       </c>
@@ -8989,7 +9001,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A278" t="s">
         <v>571</v>
       </c>
@@ -9009,7 +9021,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A279" t="s">
         <v>573</v>
       </c>
@@ -9029,7 +9041,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
         <v>575</v>
       </c>
@@ -9049,7 +9061,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A281" t="s">
         <v>577</v>
       </c>
@@ -9069,7 +9081,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A282" t="s">
         <v>579</v>
       </c>
@@ -9089,7 +9101,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A283" t="s">
         <v>581</v>
       </c>
@@ -9109,7 +9121,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A284" t="s">
         <v>583</v>
       </c>
@@ -9129,7 +9141,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A285" t="s">
         <v>585</v>
       </c>
@@ -9149,7 +9161,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
         <v>587</v>
       </c>
@@ -9169,7 +9181,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A287" t="s">
         <v>589</v>
       </c>
@@ -9189,7 +9201,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A288" t="s">
         <v>591</v>
       </c>
@@ -9209,7 +9221,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
         <v>593</v>
       </c>
@@ -9229,7 +9241,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A290" t="s">
         <v>595</v>
       </c>
@@ -9249,7 +9261,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A291" t="s">
         <v>597</v>
       </c>
@@ -9269,7 +9281,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A292" t="s">
         <v>599</v>
       </c>
@@ -9289,7 +9301,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A293" t="s">
         <v>601</v>
       </c>
@@ -9309,7 +9321,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A294" t="s">
         <v>603</v>
       </c>
@@ -9329,7 +9341,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
         <v>605</v>
       </c>
@@ -9349,7 +9361,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A296" t="s">
         <v>607</v>
       </c>
@@ -9369,7 +9381,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
         <v>609</v>
       </c>
@@ -9389,7 +9401,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
         <v>611</v>
       </c>
@@ -9409,7 +9421,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A299" t="s">
         <v>613</v>
       </c>
@@ -9429,7 +9441,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A300" t="s">
         <v>615</v>
       </c>
@@ -9449,7 +9461,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A301" t="s">
         <v>617</v>
       </c>
@@ -9469,7 +9481,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A302" t="s">
         <v>619</v>
       </c>
@@ -9489,7 +9501,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A303" t="s">
         <v>622</v>
       </c>
@@ -9509,7 +9521,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
         <v>624</v>
       </c>
@@ -9529,7 +9541,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A305" t="s">
         <v>626</v>
       </c>
@@ -9549,7 +9561,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A306" t="s">
         <v>628</v>
       </c>
@@ -9569,7 +9581,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
         <v>630</v>
       </c>
@@ -9589,7 +9601,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A308" t="s">
         <v>632</v>
       </c>
@@ -9609,7 +9621,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A309" t="s">
         <v>634</v>
       </c>
@@ -9629,7 +9641,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A310" t="s">
         <v>636</v>
       </c>
@@ -9649,7 +9661,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A311" t="s">
         <v>638</v>
       </c>
@@ -9669,7 +9681,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A312" t="s">
         <v>640</v>
       </c>
@@ -9689,7 +9701,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
         <v>642</v>
       </c>
@@ -9709,7 +9721,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A314" t="s">
         <v>644</v>
       </c>
@@ -9729,7 +9741,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A315" t="s">
         <v>646</v>
       </c>
@@ -9749,7 +9761,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
         <v>648</v>
       </c>
@@ -9769,7 +9781,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A317" t="s">
         <v>650</v>
       </c>
@@ -9789,7 +9801,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A318" t="s">
         <v>652</v>
       </c>
@@ -9809,7 +9821,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A319" t="s">
         <v>654</v>
       </c>
@@ -9829,7 +9841,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A320" t="s">
         <v>656</v>
       </c>
@@ -9849,7 +9861,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A321" t="s">
         <v>658</v>
       </c>
@@ -9869,7 +9881,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A322" t="s">
         <v>660</v>
       </c>
@@ -9889,7 +9901,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A323" t="s">
         <v>663</v>
       </c>
@@ -9909,7 +9921,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A324" t="s">
         <v>665</v>
       </c>
@@ -9929,7 +9941,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
         <v>667</v>
       </c>
@@ -9949,7 +9961,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A326" t="s">
         <v>669</v>
       </c>
@@ -9969,7 +9981,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A327" t="s">
         <v>671</v>
       </c>
@@ -9989,7 +10001,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A328" t="s">
         <v>673</v>
       </c>
@@ -10009,7 +10021,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A329" t="s">
         <v>675</v>
       </c>
@@ -10029,7 +10041,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A330" t="s">
         <v>677</v>
       </c>
@@ -10049,7 +10061,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
         <v>679</v>
       </c>
@@ -10069,7 +10081,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A332" t="s">
         <v>681</v>
       </c>
@@ -10089,7 +10101,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A333" t="s">
         <v>683</v>
       </c>
@@ -10109,7 +10121,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
         <v>685</v>
       </c>
@@ -10129,7 +10141,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A335" t="s">
         <v>687</v>
       </c>
@@ -10149,7 +10161,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A336" t="s">
         <v>689</v>
       </c>
@@ -10169,7 +10181,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A337" t="s">
         <v>691</v>
       </c>
@@ -10189,7 +10201,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A338" t="s">
         <v>693</v>
       </c>
@@ -10209,7 +10221,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A339" t="s">
         <v>695</v>
       </c>
@@ -10229,7 +10241,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A340" t="s">
         <v>697</v>
       </c>
@@ -10249,7 +10261,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A341" t="s">
         <v>699</v>
       </c>
@@ -10269,7 +10281,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A342" t="s">
         <v>701</v>
       </c>
@@ -10289,7 +10301,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
         <v>704</v>
       </c>
@@ -10309,7 +10321,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A344" t="s">
         <v>706</v>
       </c>
@@ -10329,7 +10341,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A345" t="s">
         <v>708</v>
       </c>
@@ -10349,7 +10361,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A346" t="s">
         <v>710</v>
       </c>
@@ -10369,7 +10381,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A347" t="s">
         <v>712</v>
       </c>
@@ -10389,7 +10401,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A348" t="s">
         <v>714</v>
       </c>
@@ -10409,7 +10421,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A349" t="s">
         <v>716</v>
       </c>
@@ -10429,7 +10441,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A350" t="s">
         <v>718</v>
       </c>
@@ -10449,7 +10461,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A351" t="s">
         <v>720</v>
       </c>
@@ -10469,7 +10481,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A352" t="s">
         <v>722</v>
       </c>
@@ -10489,7 +10501,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A353" t="s">
         <v>724</v>
       </c>
@@ -10509,7 +10521,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A354" t="s">
         <v>727</v>
       </c>
@@ -10529,7 +10541,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A355" t="s">
         <v>729</v>
       </c>
@@ -10549,7 +10561,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A356" t="s">
         <v>731</v>
       </c>
@@ -10569,7 +10581,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A357" t="s">
         <v>733</v>
       </c>
@@ -10589,7 +10601,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A358" t="s">
         <v>735</v>
       </c>
@@ -10609,7 +10621,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A359" t="s">
         <v>737</v>
       </c>
@@ -10629,7 +10641,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A360" t="s">
         <v>739</v>
       </c>
@@ -10649,7 +10661,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
         <v>741</v>
       </c>
@@ -10669,7 +10681,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A362" t="s">
         <v>743</v>
       </c>
@@ -10689,7 +10701,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A363" t="s">
         <v>747</v>
       </c>
@@ -10709,7 +10721,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A364" t="s">
         <v>749</v>
       </c>
@@ -10729,7 +10741,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A365" t="s">
         <v>751</v>
       </c>
@@ -10749,7 +10761,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A366" t="s">
         <v>753</v>
       </c>
@@ -10769,7 +10781,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A367" t="s">
         <v>755</v>
       </c>
@@ -10789,7 +10801,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A368" t="s">
         <v>757</v>
       </c>
@@ -10809,7 +10821,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A369" t="s">
         <v>759</v>
       </c>
@@ -10829,7 +10841,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
         <v>761</v>
       </c>
@@ -10849,7 +10861,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A371" t="s">
         <v>763</v>
       </c>
@@ -10869,7 +10881,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A372" t="s">
         <v>765</v>
       </c>
@@ -10889,7 +10901,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A373" t="s">
         <v>767</v>
       </c>
@@ -10909,7 +10921,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A374" t="s">
         <v>769</v>
       </c>
@@ -10929,7 +10941,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A375" t="s">
         <v>771</v>
       </c>
@@ -10949,7 +10961,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A376" t="s">
         <v>773</v>
       </c>
@@ -10969,7 +10981,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A377" t="s">
         <v>775</v>
       </c>
@@ -10989,7 +11001,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A378" t="s">
         <v>777</v>
       </c>
@@ -11009,7 +11021,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
         <v>779</v>
       </c>
@@ -11029,7 +11041,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A380" t="s">
         <v>781</v>
       </c>
@@ -11049,7 +11061,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A381" t="s">
         <v>783</v>
       </c>
@@ -11069,7 +11081,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A382" t="s">
         <v>785</v>
       </c>
@@ -11089,7 +11101,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A383" t="s">
         <v>788</v>
       </c>
@@ -11109,7 +11121,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A384" t="s">
         <v>790</v>
       </c>
@@ -11129,7 +11141,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A385" t="s">
         <v>792</v>
       </c>
@@ -11149,7 +11161,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A386" t="s">
         <v>794</v>
       </c>
@@ -11169,7 +11181,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A387" t="s">
         <v>796</v>
       </c>
@@ -11189,7 +11201,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A388" t="s">
         <v>798</v>
       </c>
@@ -11209,7 +11221,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A389" t="s">
         <v>800</v>
       </c>
@@ -11229,7 +11241,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A390" t="s">
         <v>802</v>
       </c>
@@ -11249,7 +11261,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A391" t="s">
         <v>804</v>
       </c>
@@ -11269,7 +11281,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A392" t="s">
         <v>806</v>
       </c>
@@ -11289,7 +11301,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A393" t="s">
         <v>808</v>
       </c>
@@ -11309,7 +11321,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A394" t="s">
         <v>810</v>
       </c>
@@ -11329,7 +11341,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A395" t="s">
         <v>812</v>
       </c>
@@ -11349,7 +11361,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A396" t="s">
         <v>814</v>
       </c>
@@ -11369,7 +11381,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
         <v>816</v>
       </c>
@@ -11389,7 +11401,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A398" t="s">
         <v>818</v>
       </c>
@@ -11409,7 +11421,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A399" t="s">
         <v>820</v>
       </c>
@@ -11429,7 +11441,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A400" t="s">
         <v>822</v>
       </c>
@@ -11449,7 +11461,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A401" t="s">
         <v>824</v>
       </c>
@@ -11469,7 +11481,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A402" t="s">
         <v>826</v>
       </c>
@@ -11489,7 +11501,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A403" t="s">
         <v>829</v>
       </c>
@@ -11509,7 +11521,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A404" t="s">
         <v>831</v>
       </c>
@@ -11529,7 +11541,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A405" t="s">
         <v>833</v>
       </c>
@@ -11549,7 +11561,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A406" t="s">
         <v>835</v>
       </c>
@@ -11569,7 +11581,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A407" t="s">
         <v>837</v>
       </c>
@@ -11589,7 +11601,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A408" t="s">
         <v>839</v>
       </c>
@@ -11609,7 +11621,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A409" t="s">
         <v>841</v>
       </c>
@@ -11629,7 +11641,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A410" t="s">
         <v>843</v>
       </c>
@@ -11649,7 +11661,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A411" t="s">
         <v>845</v>
       </c>
@@ -11669,7 +11681,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A412" t="s">
         <v>847</v>
       </c>
@@ -11689,7 +11701,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A413" t="s">
         <v>849</v>
       </c>
@@ -11709,7 +11721,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A414" t="s">
         <v>851</v>
       </c>
@@ -11729,7 +11741,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A415" t="s">
         <v>853</v>
       </c>
@@ -11749,7 +11761,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A416" t="s">
         <v>855</v>
       </c>
@@ -11769,7 +11781,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A417" t="s">
         <v>857</v>
       </c>
@@ -11789,7 +11801,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A418" t="s">
         <v>859</v>
       </c>
@@ -11809,7 +11821,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A419" t="s">
         <v>861</v>
       </c>
@@ -11829,7 +11841,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A420" t="s">
         <v>863</v>
       </c>
@@ -11849,7 +11861,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A421" t="s">
         <v>865</v>
       </c>
@@ -11869,7 +11881,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A422" t="s">
         <v>867</v>
       </c>
@@ -11889,7 +11901,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A423" t="s">
         <v>870</v>
       </c>
@@ -11909,7 +11921,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
         <v>872</v>
       </c>
@@ -11929,7 +11941,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A425" t="s">
         <v>874</v>
       </c>
@@ -11949,7 +11961,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A426" t="s">
         <v>876</v>
       </c>
@@ -11969,7 +11981,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A427" t="s">
         <v>878</v>
       </c>
@@ -11989,7 +12001,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A428" t="s">
         <v>880</v>
       </c>
@@ -12009,7 +12021,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A429" t="s">
         <v>882</v>
       </c>
@@ -12029,7 +12041,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A430" t="s">
         <v>884</v>
       </c>
@@ -12049,7 +12061,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A431" t="s">
         <v>886</v>
       </c>
@@ -12069,7 +12081,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A432" t="s">
         <v>888</v>
       </c>
@@ -12089,7 +12101,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
         <v>890</v>
       </c>
@@ -12109,7 +12121,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A434" t="s">
         <v>892</v>
       </c>
@@ -12129,7 +12141,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A435" t="s">
         <v>894</v>
       </c>
@@ -12149,7 +12161,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A436" t="s">
         <v>896</v>
       </c>
@@ -12169,7 +12181,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A437" t="s">
         <v>898</v>
       </c>
@@ -12189,7 +12201,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A438" t="s">
         <v>900</v>
       </c>
@@ -12209,7 +12221,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A439" t="s">
         <v>902</v>
       </c>
@@ -12229,7 +12241,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A440" t="s">
         <v>904</v>
       </c>
@@ -12249,7 +12261,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A441" t="s">
         <v>906</v>
       </c>
@@ -12269,7 +12281,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A442" t="s">
         <v>908</v>
       </c>
@@ -12289,7 +12301,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A443" t="s">
         <v>910</v>
       </c>
@@ -12309,7 +12321,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A444" t="s">
         <v>912</v>
       </c>
@@ -12329,7 +12341,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A445" t="s">
         <v>914</v>
       </c>
@@ -12349,7 +12361,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A446" t="s">
         <v>916</v>
       </c>
@@ -12369,7 +12381,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A447" t="s">
         <v>918</v>
       </c>
@@ -12389,7 +12401,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A448" t="s">
         <v>920</v>
       </c>
@@ -12409,7 +12421,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A449" t="s">
         <v>922</v>
       </c>
@@ -12429,7 +12441,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A450" t="s">
         <v>924</v>
       </c>
@@ -12449,7 +12461,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
         <v>926</v>
       </c>
@@ -12469,7 +12481,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A452" t="s">
         <v>928</v>
       </c>
@@ -12489,7 +12501,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A453" t="s">
         <v>930</v>
       </c>
@@ -12509,7 +12521,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A454" t="s">
         <v>932</v>
       </c>
@@ -12529,7 +12541,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A455" t="s">
         <v>934</v>
       </c>
@@ -12549,7 +12561,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A456" t="s">
         <v>936</v>
       </c>
@@ -12569,7 +12581,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
         <v>938</v>
       </c>
@@ -12589,7 +12601,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A458" t="s">
         <v>940</v>
       </c>
@@ -12609,7 +12621,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A459" t="s">
         <v>942</v>
       </c>
@@ -12629,7 +12641,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
         <v>944</v>
       </c>
@@ -12649,7 +12661,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A461" t="s">
         <v>946</v>
       </c>
@@ -12669,7 +12681,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A462" t="s">
         <v>948</v>
       </c>
@@ -12689,7 +12701,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A463" t="s">
         <v>950</v>
       </c>
@@ -12709,7 +12721,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A464" t="s">
         <v>952</v>
       </c>
@@ -12729,7 +12741,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A465" t="s">
         <v>954</v>
       </c>
@@ -12749,7 +12761,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A466" t="s">
         <v>956</v>
       </c>
@@ -12769,7 +12781,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A467" t="s">
         <v>958</v>
       </c>
@@ -12789,7 +12801,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A468" t="s">
         <v>960</v>
       </c>
@@ -12809,7 +12821,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
         <v>962</v>
       </c>
@@ -12829,7 +12841,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A470" t="s">
         <v>964</v>
       </c>
@@ -12849,7 +12861,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A471" t="s">
         <v>966</v>
       </c>
@@ -12871,14 +12883,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F459"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -12888,7 +12900,7 @@
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -12908,7 +12920,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -12928,7 +12940,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -12948,7 +12960,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -12968,7 +12980,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -12988,7 +13000,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -13008,7 +13020,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -13028,7 +13040,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -13048,7 +13060,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -13068,7 +13080,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -13088,7 +13100,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -13108,7 +13120,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -13128,7 +13140,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -13148,7 +13160,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -13168,7 +13180,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -13188,7 +13200,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -13208,7 +13220,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>42</v>
       </c>
@@ -13228,7 +13240,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -13248,7 +13260,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -13268,7 +13280,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -13288,7 +13300,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -13308,7 +13320,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -13328,7 +13340,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -13348,7 +13360,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>56</v>
       </c>
@@ -13368,7 +13380,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -13388,7 +13400,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>60</v>
       </c>
@@ -13408,7 +13420,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>62</v>
       </c>
@@ -13428,7 +13440,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>64</v>
       </c>
@@ -13448,7 +13460,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>66</v>
       </c>
@@ -13468,7 +13480,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>68</v>
       </c>
@@ -13488,7 +13500,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>70</v>
       </c>
@@ -13508,7 +13520,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>72</v>
       </c>
@@ -13528,7 +13540,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -13548,7 +13560,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>76</v>
       </c>
@@ -13568,7 +13580,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>78</v>
       </c>
@@ -13588,7 +13600,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>80</v>
       </c>
@@ -13608,7 +13620,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>82</v>
       </c>
@@ -13628,7 +13640,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>84</v>
       </c>
@@ -13648,7 +13660,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>86</v>
       </c>
@@ -13668,7 +13680,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>88</v>
       </c>
@@ -13688,7 +13700,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>90</v>
       </c>
@@ -13708,7 +13720,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -13728,7 +13740,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>96</v>
       </c>
@@ -13748,7 +13760,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>98</v>
       </c>
@@ -13768,7 +13780,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>100</v>
       </c>
@@ -13788,7 +13800,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>102</v>
       </c>
@@ -13808,7 +13820,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>104</v>
       </c>
@@ -13828,7 +13840,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>106</v>
       </c>
@@ -13848,7 +13860,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>110</v>
       </c>
@@ -13868,7 +13880,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>112</v>
       </c>
@@ -13888,7 +13900,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>114</v>
       </c>
@@ -13908,7 +13920,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>116</v>
       </c>
@@ -13928,7 +13940,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>118</v>
       </c>
@@ -13948,7 +13960,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>120</v>
       </c>
@@ -13968,7 +13980,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>122</v>
       </c>
@@ -13988,7 +14000,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>124</v>
       </c>
@@ -14008,7 +14020,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>126</v>
       </c>
@@ -14028,7 +14040,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>128</v>
       </c>
@@ -14048,7 +14060,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>130</v>
       </c>
@@ -14068,7 +14080,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>132</v>
       </c>
@@ -14088,7 +14100,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>134</v>
       </c>
@@ -14108,7 +14120,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>136</v>
       </c>
@@ -14128,7 +14140,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>138</v>
       </c>
@@ -14148,7 +14160,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>140</v>
       </c>
@@ -14168,7 +14180,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>142</v>
       </c>
@@ -14188,7 +14200,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>144</v>
       </c>
@@ -14208,7 +14220,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>146</v>
       </c>
@@ -14228,7 +14240,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>148</v>
       </c>
@@ -14248,7 +14260,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>150</v>
       </c>
@@ -14268,7 +14280,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>152</v>
       </c>
@@ -14288,7 +14300,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>154</v>
       </c>
@@ -14308,7 +14320,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>156</v>
       </c>
@@ -14328,7 +14340,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>158</v>
       </c>
@@ -14348,7 +14360,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>160</v>
       </c>
@@ -14368,7 +14380,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>162</v>
       </c>
@@ -14388,7 +14400,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>164</v>
       </c>
@@ -14408,7 +14420,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>166</v>
       </c>
@@ -14428,7 +14440,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>168</v>
       </c>
@@ -14448,7 +14460,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>170</v>
       </c>
@@ -14468,7 +14480,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>172</v>
       </c>
@@ -14488,7 +14500,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>176</v>
       </c>
@@ -14508,7 +14520,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>178</v>
       </c>
@@ -14528,7 +14540,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>180</v>
       </c>
@@ -14548,7 +14560,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>182</v>
       </c>
@@ -14568,7 +14580,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>184</v>
       </c>
@@ -14588,7 +14600,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>186</v>
       </c>
@@ -14608,7 +14620,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>188</v>
       </c>
@@ -14628,7 +14640,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>190</v>
       </c>
@@ -14648,7 +14660,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>192</v>
       </c>
@@ -14668,7 +14680,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>194</v>
       </c>
@@ -14688,7 +14700,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>196</v>
       </c>
@@ -14708,7 +14720,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>198</v>
       </c>
@@ -14728,7 +14740,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>200</v>
       </c>
@@ -14748,7 +14760,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>202</v>
       </c>
@@ -14768,7 +14780,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>204</v>
       </c>
@@ -14788,7 +14800,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>206</v>
       </c>
@@ -14808,7 +14820,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>208</v>
       </c>
@@ -14828,7 +14840,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>210</v>
       </c>
@@ -14848,7 +14860,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>212</v>
       </c>
@@ -14868,7 +14880,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>214</v>
       </c>
@@ -14888,7 +14900,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>216</v>
       </c>
@@ -14908,7 +14920,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>218</v>
       </c>
@@ -14928,7 +14940,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>220</v>
       </c>
@@ -14948,7 +14960,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>222</v>
       </c>
@@ -14968,7 +14980,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>224</v>
       </c>
@@ -14988,7 +15000,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>226</v>
       </c>
@@ -15008,7 +15020,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>228</v>
       </c>
@@ -15028,7 +15040,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>230</v>
       </c>
@@ -15048,7 +15060,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>232</v>
       </c>
@@ -15068,7 +15080,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>234</v>
       </c>
@@ -15088,7 +15100,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>237</v>
       </c>
@@ -15108,7 +15120,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>239</v>
       </c>
@@ -15128,7 +15140,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>241</v>
       </c>
@@ -15148,7 +15160,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>243</v>
       </c>
@@ -15168,7 +15180,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>245</v>
       </c>
@@ -15188,7 +15200,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>247</v>
       </c>
@@ -15208,7 +15220,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>249</v>
       </c>
@@ -15228,7 +15240,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>251</v>
       </c>
@@ -15248,7 +15260,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>253</v>
       </c>
@@ -15268,7 +15280,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>255</v>
       </c>
@@ -15288,7 +15300,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>257</v>
       </c>
@@ -15308,7 +15320,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>259</v>
       </c>
@@ -15328,7 +15340,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>261</v>
       </c>
@@ -15348,7 +15360,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>263</v>
       </c>
@@ -15368,7 +15380,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>265</v>
       </c>
@@ -15388,7 +15400,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>267</v>
       </c>
@@ -15408,7 +15420,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>269</v>
       </c>
@@ -15428,7 +15440,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>271</v>
       </c>
@@ -15448,7 +15460,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>273</v>
       </c>
@@ -15468,7 +15480,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>275</v>
       </c>
@@ -15488,7 +15500,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>277</v>
       </c>
@@ -15508,7 +15520,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>279</v>
       </c>
@@ -15528,7 +15540,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>281</v>
       </c>
@@ -15548,7 +15560,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>283</v>
       </c>
@@ -15568,7 +15580,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>285</v>
       </c>
@@ -15588,7 +15600,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>287</v>
       </c>
@@ -15608,7 +15620,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>289</v>
       </c>
@@ -15628,7 +15640,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>291</v>
       </c>
@@ -15648,7 +15660,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>293</v>
       </c>
@@ -15668,7 +15680,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>295</v>
       </c>
@@ -15688,7 +15700,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>297</v>
       </c>
@@ -15708,7 +15720,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>299</v>
       </c>
@@ -15728,7 +15740,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>301</v>
       </c>
@@ -15748,7 +15760,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>303</v>
       </c>
@@ -15768,7 +15780,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>305</v>
       </c>
@@ -15788,7 +15800,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>307</v>
       </c>
@@ -15808,7 +15820,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>309</v>
       </c>
@@ -15828,7 +15840,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>311</v>
       </c>
@@ -15848,7 +15860,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>313</v>
       </c>
@@ -15868,7 +15880,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>315</v>
       </c>
@@ -15888,7 +15900,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>317</v>
       </c>
@@ -15908,7 +15920,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>319</v>
       </c>
@@ -15928,7 +15940,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>321</v>
       </c>
@@ -15948,7 +15960,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>323</v>
       </c>
@@ -15968,7 +15980,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>325</v>
       </c>
@@ -15988,7 +16000,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>327</v>
       </c>
@@ -16008,7 +16020,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>329</v>
       </c>
@@ -16028,7 +16040,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>331</v>
       </c>
@@ -16048,7 +16060,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>333</v>
       </c>
@@ -16068,7 +16080,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>335</v>
       </c>
@@ -16088,7 +16100,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>339</v>
       </c>
@@ -16108,7 +16120,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>341</v>
       </c>
@@ -16128,7 +16140,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>343</v>
       </c>
@@ -16148,7 +16160,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>345</v>
       </c>
@@ -16168,7 +16180,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>347</v>
       </c>
@@ -16188,7 +16200,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>349</v>
       </c>
@@ -16208,7 +16220,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>351</v>
       </c>
@@ -16228,7 +16240,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>353</v>
       </c>
@@ -16248,7 +16260,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>355</v>
       </c>
@@ -16268,7 +16280,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>357</v>
       </c>
@@ -16288,7 +16300,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>359</v>
       </c>
@@ -16308,7 +16320,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>361</v>
       </c>
@@ -16328,7 +16340,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>363</v>
       </c>
@@ -16348,7 +16360,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>367</v>
       </c>
@@ -16368,7 +16380,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>369</v>
       </c>
@@ -16388,7 +16400,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>371</v>
       </c>
@@ -16408,7 +16420,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>373</v>
       </c>
@@ -16428,7 +16440,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>375</v>
       </c>
@@ -16448,7 +16460,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>377</v>
       </c>
@@ -16468,7 +16480,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>379</v>
       </c>
@@ -16488,7 +16500,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>381</v>
       </c>
@@ -16508,7 +16520,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>383</v>
       </c>
@@ -16528,7 +16540,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>385</v>
       </c>
@@ -16548,7 +16560,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>387</v>
       </c>
@@ -16568,7 +16580,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>389</v>
       </c>
@@ -16588,7 +16600,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>391</v>
       </c>
@@ -16608,7 +16620,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>393</v>
       </c>
@@ -16628,7 +16640,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>395</v>
       </c>
@@ -16648,7 +16660,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>397</v>
       </c>
@@ -16668,7 +16680,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>399</v>
       </c>
@@ -16688,7 +16700,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>401</v>
       </c>
@@ -16708,7 +16720,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>403</v>
       </c>
@@ -16728,7 +16740,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>405</v>
       </c>
@@ -16748,7 +16760,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>407</v>
       </c>
@@ -16768,7 +16780,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>409</v>
       </c>
@@ -16788,7 +16800,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>411</v>
       </c>
@@ -16808,7 +16820,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>413</v>
       </c>
@@ -16828,7 +16840,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
         <v>415</v>
       </c>
@@ -16848,7 +16860,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
         <v>417</v>
       </c>
@@ -16868,7 +16880,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>419</v>
       </c>
@@ -16888,7 +16900,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>421</v>
       </c>
@@ -16908,7 +16920,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
         <v>423</v>
       </c>
@@ -16928,7 +16940,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
         <v>425</v>
       </c>
@@ -16948,7 +16960,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
         <v>427</v>
       </c>
@@ -16968,7 +16980,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
         <v>429</v>
       </c>
@@ -16988,7 +17000,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
         <v>431</v>
       </c>
@@ -17008,7 +17020,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
         <v>433</v>
       </c>
@@ -17028,7 +17040,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
         <v>435</v>
       </c>
@@ -17048,7 +17060,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
         <v>437</v>
       </c>
@@ -17068,7 +17080,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
         <v>440</v>
       </c>
@@ -17088,7 +17100,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
         <v>442</v>
       </c>
@@ -17108,7 +17120,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
         <v>444</v>
       </c>
@@ -17128,7 +17140,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
         <v>446</v>
       </c>
@@ -17148,7 +17160,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
         <v>448</v>
       </c>
@@ -17168,7 +17180,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
         <v>450</v>
       </c>
@@ -17188,7 +17200,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
         <v>452</v>
       </c>
@@ -17208,7 +17220,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
         <v>454</v>
       </c>
@@ -17228,7 +17240,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
         <v>456</v>
       </c>
@@ -17248,7 +17260,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
         <v>458</v>
       </c>
@@ -17268,7 +17280,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
         <v>460</v>
       </c>
@@ -17288,7 +17300,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
         <v>462</v>
       </c>
@@ -17308,7 +17320,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
         <v>464</v>
       </c>
@@ -17328,7 +17340,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
         <v>466</v>
       </c>
@@ -17348,7 +17360,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
         <v>468</v>
       </c>
@@ -17368,7 +17380,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
         <v>470</v>
       </c>
@@ -17388,7 +17400,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
         <v>472</v>
       </c>
@@ -17408,7 +17420,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
         <v>474</v>
       </c>
@@ -17428,7 +17440,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
         <v>476</v>
       </c>
@@ -17448,7 +17460,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
         <v>478</v>
       </c>
@@ -17468,7 +17480,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
         <v>480</v>
       </c>
@@ -17488,7 +17500,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
         <v>482</v>
       </c>
@@ -17508,7 +17520,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
         <v>484</v>
       </c>
@@ -17528,7 +17540,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
         <v>486</v>
       </c>
@@ -17548,7 +17560,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A234" t="s">
         <v>488</v>
       </c>
@@ -17568,7 +17580,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
         <v>490</v>
       </c>
@@ -17588,7 +17600,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A236" t="s">
         <v>492</v>
       </c>
@@ -17608,7 +17620,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
         <v>494</v>
       </c>
@@ -17628,7 +17640,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A238" t="s">
         <v>498</v>
       </c>
@@ -17648,7 +17660,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A239" t="s">
         <v>500</v>
       </c>
@@ -17668,7 +17680,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A240" t="s">
         <v>502</v>
       </c>
@@ -17688,7 +17700,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
         <v>504</v>
       </c>
@@ -17708,7 +17720,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
         <v>506</v>
       </c>
@@ -17728,7 +17740,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
         <v>508</v>
       </c>
@@ -17748,7 +17760,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
         <v>510</v>
       </c>
@@ -17768,7 +17780,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
         <v>512</v>
       </c>
@@ -17788,7 +17800,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A246" t="s">
         <v>514</v>
       </c>
@@ -17808,7 +17820,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
         <v>516</v>
       </c>
@@ -17828,7 +17840,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
         <v>518</v>
       </c>
@@ -17848,7 +17860,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
         <v>520</v>
       </c>
@@ -17868,7 +17880,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
         <v>522</v>
       </c>
@@ -17888,7 +17900,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
         <v>524</v>
       </c>
@@ -17908,7 +17920,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
         <v>526</v>
       </c>
@@ -17928,7 +17940,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
         <v>528</v>
       </c>
@@ -17948,7 +17960,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A254" t="s">
         <v>530</v>
       </c>
@@ -17968,7 +17980,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
         <v>532</v>
       </c>
@@ -17988,7 +18000,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A256" t="s">
         <v>534</v>
       </c>
@@ -18008,7 +18020,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
         <v>536</v>
       </c>
@@ -18028,7 +18040,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A258" t="s">
         <v>538</v>
       </c>
@@ -18048,7 +18060,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
         <v>541</v>
       </c>
@@ -18068,7 +18080,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
         <v>543</v>
       </c>
@@ -18088,7 +18100,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
         <v>545</v>
       </c>
@@ -18108,7 +18120,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
         <v>547</v>
       </c>
@@ -18128,7 +18140,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A263" t="s">
         <v>549</v>
       </c>
@@ -18148,7 +18160,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A264" t="s">
         <v>551</v>
       </c>
@@ -18168,7 +18180,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
         <v>553</v>
       </c>
@@ -18188,7 +18200,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
         <v>555</v>
       </c>
@@ -18208,7 +18220,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A267" t="s">
         <v>557</v>
       </c>
@@ -18228,7 +18240,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
         <v>559</v>
       </c>
@@ -18248,7 +18260,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A269" t="s">
         <v>561</v>
       </c>
@@ -18268,7 +18280,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A270" t="s">
         <v>563</v>
       </c>
@@ -18288,7 +18300,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
         <v>565</v>
       </c>
@@ -18308,7 +18320,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A272" t="s">
         <v>567</v>
       </c>
@@ -18328,7 +18340,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
         <v>569</v>
       </c>
@@ -18348,7 +18360,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A274" t="s">
         <v>571</v>
       </c>
@@ -18368,7 +18380,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A275" t="s">
         <v>575</v>
       </c>
@@ -18388,7 +18400,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A276" t="s">
         <v>577</v>
       </c>
@@ -18408,7 +18420,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
         <v>579</v>
       </c>
@@ -18428,7 +18440,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A278" t="s">
         <v>581</v>
       </c>
@@ -18448,7 +18460,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A279" t="s">
         <v>583</v>
       </c>
@@ -18468,7 +18480,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
         <v>585</v>
       </c>
@@ -18488,7 +18500,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A281" t="s">
         <v>587</v>
       </c>
@@ -18508,7 +18520,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A282" t="s">
         <v>589</v>
       </c>
@@ -18528,7 +18540,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A283" t="s">
         <v>591</v>
       </c>
@@ -18548,7 +18560,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A284" t="s">
         <v>593</v>
       </c>
@@ -18568,7 +18580,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A285" t="s">
         <v>595</v>
       </c>
@@ -18588,7 +18600,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
         <v>597</v>
       </c>
@@ -18608,7 +18620,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A287" t="s">
         <v>599</v>
       </c>
@@ -18628,7 +18640,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A288" t="s">
         <v>601</v>
       </c>
@@ -18648,7 +18660,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
         <v>603</v>
       </c>
@@ -18668,7 +18680,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A290" t="s">
         <v>605</v>
       </c>
@@ -18688,7 +18700,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A291" t="s">
         <v>607</v>
       </c>
@@ -18708,7 +18720,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A292" t="s">
         <v>609</v>
       </c>
@@ -18728,7 +18740,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A293" t="s">
         <v>611</v>
       </c>
@@ -18748,7 +18760,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A294" t="s">
         <v>613</v>
       </c>
@@ -18768,7 +18780,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
         <v>615</v>
       </c>
@@ -18788,7 +18800,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A296" t="s">
         <v>617</v>
       </c>
@@ -18808,7 +18820,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
         <v>619</v>
       </c>
@@ -18828,7 +18840,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
         <v>622</v>
       </c>
@@ -18848,7 +18860,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A299" t="s">
         <v>624</v>
       </c>
@@ -18868,7 +18880,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A300" t="s">
         <v>626</v>
       </c>
@@ -18888,7 +18900,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A301" t="s">
         <v>628</v>
       </c>
@@ -18908,7 +18920,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A302" t="s">
         <v>630</v>
       </c>
@@ -18928,7 +18940,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A303" t="s">
         <v>632</v>
       </c>
@@ -18948,7 +18960,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
         <v>634</v>
       </c>
@@ -18968,7 +18980,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A305" t="s">
         <v>636</v>
       </c>
@@ -18988,7 +19000,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A306" t="s">
         <v>638</v>
       </c>
@@ -19008,7 +19020,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
         <v>640</v>
       </c>
@@ -19028,7 +19040,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A308" t="s">
         <v>642</v>
       </c>
@@ -19048,7 +19060,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A309" t="s">
         <v>644</v>
       </c>
@@ -19068,7 +19080,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A310" t="s">
         <v>646</v>
       </c>
@@ -19088,7 +19100,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A311" t="s">
         <v>648</v>
       </c>
@@ -19108,7 +19120,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A312" t="s">
         <v>650</v>
       </c>
@@ -19128,7 +19140,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
         <v>652</v>
       </c>
@@ -19148,7 +19160,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A314" t="s">
         <v>654</v>
       </c>
@@ -19168,7 +19180,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A315" t="s">
         <v>656</v>
       </c>
@@ -19188,7 +19200,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
         <v>658</v>
       </c>
@@ -19208,7 +19220,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A317" t="s">
         <v>660</v>
       </c>
@@ -19228,7 +19240,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A318" t="s">
         <v>663</v>
       </c>
@@ -19248,7 +19260,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A319" t="s">
         <v>665</v>
       </c>
@@ -19268,7 +19280,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A320" t="s">
         <v>667</v>
       </c>
@@ -19288,7 +19300,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A321" t="s">
         <v>669</v>
       </c>
@@ -19308,7 +19320,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A322" t="s">
         <v>671</v>
       </c>
@@ -19328,7 +19340,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A323" t="s">
         <v>673</v>
       </c>
@@ -19348,7 +19360,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A324" t="s">
         <v>675</v>
       </c>
@@ -19368,7 +19380,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
         <v>677</v>
       </c>
@@ -19388,7 +19400,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A326" t="s">
         <v>679</v>
       </c>
@@ -19408,7 +19420,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A327" t="s">
         <v>681</v>
       </c>
@@ -19428,7 +19440,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A328" t="s">
         <v>683</v>
       </c>
@@ -19448,7 +19460,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A329" t="s">
         <v>685</v>
       </c>
@@ -19468,7 +19480,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A330" t="s">
         <v>689</v>
       </c>
@@ -19488,7 +19500,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
         <v>691</v>
       </c>
@@ -19508,7 +19520,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A332" t="s">
         <v>693</v>
       </c>
@@ -19528,7 +19540,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A333" t="s">
         <v>695</v>
       </c>
@@ -19548,7 +19560,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
         <v>697</v>
       </c>
@@ -19568,7 +19580,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A335" t="s">
         <v>699</v>
       </c>
@@ -19588,7 +19600,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A336" t="s">
         <v>701</v>
       </c>
@@ -19608,7 +19620,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A337" t="s">
         <v>704</v>
       </c>
@@ -19628,7 +19640,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A338" t="s">
         <v>706</v>
       </c>
@@ -19648,7 +19660,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A339" t="s">
         <v>710</v>
       </c>
@@ -19668,7 +19680,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A340" t="s">
         <v>712</v>
       </c>
@@ -19688,7 +19700,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A341" t="s">
         <v>714</v>
       </c>
@@ -19708,7 +19720,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A342" t="s">
         <v>716</v>
       </c>
@@ -19728,7 +19740,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
         <v>718</v>
       </c>
@@ -19748,7 +19760,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A344" t="s">
         <v>720</v>
       </c>
@@ -19768,7 +19780,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A345" t="s">
         <v>722</v>
       </c>
@@ -19788,7 +19800,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A346" t="s">
         <v>727</v>
       </c>
@@ -19808,7 +19820,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A347" t="s">
         <v>729</v>
       </c>
@@ -19828,7 +19840,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A348" t="s">
         <v>731</v>
       </c>
@@ -19848,7 +19860,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A349" t="s">
         <v>733</v>
       </c>
@@ -19868,7 +19880,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A350" t="s">
         <v>735</v>
       </c>
@@ -19888,7 +19900,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A351" t="s">
         <v>737</v>
       </c>
@@ -19908,7 +19920,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A352" t="s">
         <v>739</v>
       </c>
@@ -19928,7 +19940,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A353" t="s">
         <v>741</v>
       </c>
@@ -19948,7 +19960,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A354" t="s">
         <v>743</v>
       </c>
@@ -19968,7 +19980,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A355" t="s">
         <v>747</v>
       </c>
@@ -19988,7 +20000,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A356" t="s">
         <v>749</v>
       </c>
@@ -20008,7 +20020,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A357" t="s">
         <v>751</v>
       </c>
@@ -20028,7 +20040,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A358" t="s">
         <v>753</v>
       </c>
@@ -20048,7 +20060,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A359" t="s">
         <v>755</v>
       </c>
@@ -20068,7 +20080,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A360" t="s">
         <v>757</v>
       </c>
@@ -20088,7 +20100,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
         <v>759</v>
       </c>
@@ -20108,7 +20120,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A362" t="s">
         <v>761</v>
       </c>
@@ -20128,7 +20140,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A363" t="s">
         <v>763</v>
       </c>
@@ -20148,7 +20160,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A364" t="s">
         <v>767</v>
       </c>
@@ -20168,7 +20180,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A365" t="s">
         <v>769</v>
       </c>
@@ -20188,7 +20200,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A366" t="s">
         <v>771</v>
       </c>
@@ -20208,7 +20220,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A367" t="s">
         <v>773</v>
       </c>
@@ -20228,7 +20240,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A368" t="s">
         <v>775</v>
       </c>
@@ -20248,7 +20260,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A369" t="s">
         <v>777</v>
       </c>
@@ -20268,7 +20280,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
         <v>779</v>
       </c>
@@ -20288,7 +20300,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A371" t="s">
         <v>781</v>
       </c>
@@ -20308,7 +20320,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A372" t="s">
         <v>783</v>
       </c>
@@ -20328,7 +20340,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A373" t="s">
         <v>785</v>
       </c>
@@ -20348,7 +20360,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A374" t="s">
         <v>788</v>
       </c>
@@ -20368,7 +20380,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A375" t="s">
         <v>790</v>
       </c>
@@ -20388,7 +20400,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A376" t="s">
         <v>792</v>
       </c>
@@ -20408,7 +20420,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A377" t="s">
         <v>794</v>
       </c>
@@ -20428,7 +20440,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A378" t="s">
         <v>796</v>
       </c>
@@ -20448,7 +20460,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
         <v>798</v>
       </c>
@@ -20468,7 +20480,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A380" t="s">
         <v>800</v>
       </c>
@@ -20488,7 +20500,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A381" t="s">
         <v>802</v>
       </c>
@@ -20508,7 +20520,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A382" t="s">
         <v>806</v>
       </c>
@@ -20528,7 +20540,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A383" t="s">
         <v>808</v>
       </c>
@@ -20548,7 +20560,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A384" t="s">
         <v>810</v>
       </c>
@@ -20568,7 +20580,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A385" t="s">
         <v>812</v>
       </c>
@@ -20588,7 +20600,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A386" t="s">
         <v>814</v>
       </c>
@@ -20608,7 +20620,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A387" t="s">
         <v>816</v>
       </c>
@@ -20628,7 +20640,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A388" t="s">
         <v>818</v>
       </c>
@@ -20648,7 +20660,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A389" t="s">
         <v>820</v>
       </c>
@@ -20668,7 +20680,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A390" t="s">
         <v>822</v>
       </c>
@@ -20688,7 +20700,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A391" t="s">
         <v>824</v>
       </c>
@@ -20708,7 +20720,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A392" t="s">
         <v>826</v>
       </c>
@@ -20728,7 +20740,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A393" t="s">
         <v>829</v>
       </c>
@@ -20748,7 +20760,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A394" t="s">
         <v>831</v>
       </c>
@@ -20768,7 +20780,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A395" t="s">
         <v>833</v>
       </c>
@@ -20788,7 +20800,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A396" t="s">
         <v>835</v>
       </c>
@@ -20808,7 +20820,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
         <v>837</v>
       </c>
@@ -20828,7 +20840,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A398" t="s">
         <v>839</v>
       </c>
@@ -20848,7 +20860,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A399" t="s">
         <v>843</v>
       </c>
@@ -20868,7 +20880,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A400" t="s">
         <v>845</v>
       </c>
@@ -20888,7 +20900,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A401" t="s">
         <v>847</v>
       </c>
@@ -20908,7 +20920,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A402" t="s">
         <v>849</v>
       </c>
@@ -20928,7 +20940,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A403" t="s">
         <v>851</v>
       </c>
@@ -20948,7 +20960,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A404" t="s">
         <v>853</v>
       </c>
@@ -20968,7 +20980,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A405" t="s">
         <v>855</v>
       </c>
@@ -20988,7 +21000,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A406" t="s">
         <v>857</v>
       </c>
@@ -21008,7 +21020,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A407" t="s">
         <v>859</v>
       </c>
@@ -21028,7 +21040,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A408" t="s">
         <v>861</v>
       </c>
@@ -21048,7 +21060,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A409" t="s">
         <v>863</v>
       </c>
@@ -21068,7 +21080,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A410" t="s">
         <v>865</v>
       </c>
@@ -21088,7 +21100,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A411" t="s">
         <v>867</v>
       </c>
@@ -21108,7 +21120,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A412" t="s">
         <v>870</v>
       </c>
@@ -21128,7 +21140,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A413" t="s">
         <v>872</v>
       </c>
@@ -21148,7 +21160,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A414" t="s">
         <v>874</v>
       </c>
@@ -21168,7 +21180,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A415" t="s">
         <v>876</v>
       </c>
@@ -21188,7 +21200,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A416" t="s">
         <v>878</v>
       </c>
@@ -21208,7 +21220,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A417" t="s">
         <v>880</v>
       </c>
@@ -21228,7 +21240,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A418" t="s">
         <v>882</v>
       </c>
@@ -21248,7 +21260,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A419" t="s">
         <v>884</v>
       </c>
@@ -21268,7 +21280,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A420" t="s">
         <v>886</v>
       </c>
@@ -21288,7 +21300,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A421" t="s">
         <v>888</v>
       </c>
@@ -21308,7 +21320,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A422" t="s">
         <v>890</v>
       </c>
@@ -21328,7 +21340,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A423" t="s">
         <v>892</v>
       </c>
@@ -21348,7 +21360,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
         <v>894</v>
       </c>
@@ -21368,7 +21380,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A425" t="s">
         <v>896</v>
       </c>
@@ -21388,7 +21400,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A426" t="s">
         <v>898</v>
       </c>
@@ -21408,7 +21420,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A427" t="s">
         <v>900</v>
       </c>
@@ -21428,7 +21440,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A428" t="s">
         <v>902</v>
       </c>
@@ -21448,7 +21460,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A429" t="s">
         <v>904</v>
       </c>
@@ -21468,7 +21480,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A430" t="s">
         <v>906</v>
       </c>
@@ -21488,7 +21500,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A431" t="s">
         <v>908</v>
       </c>
@@ -21508,7 +21520,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A432" t="s">
         <v>910</v>
       </c>
@@ -21528,7 +21540,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
         <v>912</v>
       </c>
@@ -21548,7 +21560,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A434" t="s">
         <v>914</v>
       </c>
@@ -21568,7 +21580,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A435" t="s">
         <v>918</v>
       </c>
@@ -21588,7 +21600,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A436" t="s">
         <v>920</v>
       </c>
@@ -21608,7 +21620,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A437" t="s">
         <v>922</v>
       </c>
@@ -21628,7 +21640,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A438" t="s">
         <v>924</v>
       </c>
@@ -21648,7 +21660,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A439" t="s">
         <v>926</v>
       </c>
@@ -21668,7 +21680,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A440" t="s">
         <v>928</v>
       </c>
@@ -21688,7 +21700,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A441" t="s">
         <v>930</v>
       </c>
@@ -21708,7 +21720,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A442" t="s">
         <v>932</v>
       </c>
@@ -21728,7 +21740,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A443" t="s">
         <v>934</v>
       </c>
@@ -21748,7 +21760,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A444" t="s">
         <v>936</v>
       </c>
@@ -21768,7 +21780,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A445" t="s">
         <v>938</v>
       </c>
@@ -21788,7 +21800,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A446" t="s">
         <v>940</v>
       </c>
@@ -21808,7 +21820,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A447" t="s">
         <v>942</v>
       </c>
@@ -21828,7 +21840,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A448" t="s">
         <v>944</v>
       </c>
@@ -21848,7 +21860,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A449" t="s">
         <v>946</v>
       </c>
@@ -21868,7 +21880,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A450" t="s">
         <v>948</v>
       </c>
@@ -21888,7 +21900,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
         <v>950</v>
       </c>
@@ -21908,7 +21920,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A452" t="s">
         <v>952</v>
       </c>
@@ -21928,7 +21940,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A453" t="s">
         <v>954</v>
       </c>
@@ -21948,7 +21960,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A454" t="s">
         <v>956</v>
       </c>
@@ -21968,7 +21980,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A455" t="s">
         <v>958</v>
       </c>
@@ -21988,7 +22000,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A456" t="s">
         <v>960</v>
       </c>
@@ -22008,7 +22020,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
         <v>962</v>
       </c>
@@ -22028,7 +22040,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A458" t="s">
         <v>964</v>
       </c>
@@ -22048,7 +22060,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A459" t="s">
         <v>966</v>
       </c>
@@ -22070,14 +22082,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -22086,7 +22098,7 @@
     <col min="5" max="5" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -22103,7 +22115,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -22120,7 +22132,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>108</v>
       </c>
@@ -22137,7 +22149,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>365</v>
       </c>
@@ -22154,7 +22166,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>496</v>
       </c>
@@ -22171,7 +22183,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>573</v>
       </c>
@@ -22188,7 +22200,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>687</v>
       </c>
@@ -22205,7 +22217,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>708</v>
       </c>
@@ -22222,7 +22234,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>765</v>
       </c>
@@ -22239,7 +22251,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>841</v>
       </c>
@@ -22256,7 +22268,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>916</v>
       </c>
@@ -22275,14 +22287,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -22292,7 +22304,7 @@
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -22312,7 +22324,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>724</v>
       </c>
@@ -22332,7 +22344,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>804</v>
       </c>
@@ -22354,20 +22366,20 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>974</v>
       </c>
@@ -22375,7 +22387,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>976</v>
       </c>
@@ -22383,7 +22395,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>978</v>
       </c>
@@ -22391,7 +22403,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>979</v>
       </c>
@@ -22399,7 +22411,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>980</v>
       </c>
@@ -22407,7 +22419,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>981</v>
       </c>
@@ -22415,7 +22427,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>982</v>
       </c>
@@ -22425,21 +22437,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>984</v>
       </c>
@@ -22450,7 +22462,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>986</v>
       </c>
@@ -22461,7 +22473,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>987</v>
       </c>
@@ -22472,7 +22484,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>988</v>
       </c>
@@ -22483,7 +22495,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>989</v>
       </c>
@@ -22494,7 +22506,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>990</v>
       </c>
@@ -22505,7 +22517,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>991</v>
       </c>
@@ -22516,7 +22528,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>992</v>
       </c>
@@ -22527,7 +22539,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>993</v>
       </c>
@@ -22538,7 +22550,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>994</v>
       </c>
@@ -22549,7 +22561,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>995</v>
       </c>
@@ -22562,6 +22574,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>